--- a/data/Aerosol 13 Week Production Material Summary Report 73126_Co-Man Added.xlsx
+++ b/data/Aerosol 13 Week Production Material Summary Report 73126_Co-Man Added.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alamancefoods-my.sharepoint.com/personal/balapradeepkonda_alamancefoods_com/Documents/Documents/GitHub/Bala_Can_SupplyChain/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19614F4D-8348-4A51-A9DB-F5344181D6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{19614F4D-8348-4A51-A9DB-F5344181D6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E10DD69C-D0D0-473D-9415-DCAEAD6CB5CA}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D53C0C4F-A51A-4C65-852A-55F2E87F12A7}"/>
+    <workbookView xWindow="-19476" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{D53C0C4F-A51A-4C65-852A-55F2E87F12A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Club Pack Biweekly Fluid" sheetId="1" r:id="rId1"/>
@@ -2976,7 +2976,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3013,6 +3013,9 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -40482,27 +40485,27 @@
       <c r="S432" s="4">
         <v>0</v>
       </c>
-      <c r="T432" s="8">
+      <c r="T432" s="13">
         <v>35000</v>
       </c>
-      <c r="U432" s="8">
+      <c r="U432" s="13">
         <v>40000</v>
       </c>
-      <c r="V432" s="8">
+      <c r="V432" s="13">
         <v>40000</v>
       </c>
-      <c r="W432" s="8">
+      <c r="W432" s="13">
         <v>40000</v>
       </c>
-      <c r="X432" s="8">
+      <c r="X432" s="13">
         <v>40000</v>
       </c>
-      <c r="Y432" s="8"/>
-      <c r="Z432" s="8"/>
-      <c r="AA432" s="8">
+      <c r="Y432" s="13"/>
+      <c r="Z432" s="13"/>
+      <c r="AA432" s="13">
         <v>30000</v>
       </c>
-      <c r="AB432" s="8">
+      <c r="AB432" s="13">
         <v>30000</v>
       </c>
       <c r="AC432" s="8"/>
@@ -40565,31 +40568,31 @@
       <c r="S433" s="4">
         <v>0</v>
       </c>
-      <c r="T433" s="8">
+      <c r="T433" s="13">
         <v>35000</v>
       </c>
-      <c r="U433" s="8">
+      <c r="U433" s="13">
         <v>40000</v>
       </c>
-      <c r="V433" s="8">
+      <c r="V433" s="13">
         <v>40000</v>
       </c>
-      <c r="W433" s="8">
+      <c r="W433" s="13">
         <v>40000</v>
       </c>
-      <c r="X433" s="8">
+      <c r="X433" s="13">
         <v>40000</v>
       </c>
-      <c r="Y433" s="8">
+      <c r="Y433" s="13">
         <v>40000</v>
       </c>
-      <c r="Z433" s="8">
+      <c r="Z433" s="13">
         <v>40000</v>
       </c>
-      <c r="AA433" s="8">
+      <c r="AA433" s="13">
         <v>40000</v>
       </c>
-      <c r="AB433" s="8">
+      <c r="AB433" s="13">
         <v>40000</v>
       </c>
     </row>
